--- a/data/trans_orig/Q61A-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Q61A-Habitat-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Número medio de meses que lleva en paro</t>
+          <t>Número medio de meses que lleva en paro (tasa de respuesta: 95,13%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,7 +716,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,23; 5,55</t>
+          <t>3,27; 5,78</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -726,52 +726,52 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15,46; 23,34</t>
+          <t>15,18; 23,05</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7,21; 16,59</t>
+          <t>7,44; 16,99</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,93; 7,74</t>
+          <t>5,0; 7,76</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,07; 22,32</t>
+          <t>13,92; 22,3</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,73; 23,92</t>
+          <t>14,61; 24,52</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>15,08; 24,07</t>
+          <t>15,14; 24,52</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,45; 6,32</t>
+          <t>4,48; 6,46</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12,76; 18,49</t>
+          <t>12,86; 18,3</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16,04; 22,15</t>
+          <t>15,93; 21,82</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>12,91; 19,54</t>
+          <t>12,73; 19,5</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,89; 17,01</t>
+          <t>4,72; 16,25</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>12,69; 17,7</t>
+          <t>12,8; 17,69</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17,78; 23,99</t>
+          <t>17,95; 24,05</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13,28; 26,03</t>
+          <t>13,42; 26,22</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,31; 22,29</t>
+          <t>7,07; 21,48</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,53; 18,37</t>
+          <t>13,48; 18,43</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,71; 28,62</t>
+          <t>19,68; 28,21</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>16,24; 28,46</t>
+          <t>16,16; 27,32</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,64; 15,83</t>
+          <t>6,74; 14,81</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13,63; 16,89</t>
+          <t>13,63; 17,06</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19,51; 25,12</t>
+          <t>19,71; 24,67</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>16,27; 24,23</t>
+          <t>16,24; 24,91</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,91; 9,56</t>
+          <t>4,81; 9,75</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12,06; 17,1</t>
+          <t>12,04; 17,23</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13,92; 19,6</t>
+          <t>13,72; 19,53</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>15,96; 28,6</t>
+          <t>16,29; 29,91</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,11; 8,1</t>
+          <t>4,08; 8,03</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,69; 21,36</t>
+          <t>13,54; 20,81</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15,94; 24,52</t>
+          <t>16,17; 24,36</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>22,19; 42,64</t>
+          <t>21,99; 43,59</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,95; 8,13</t>
+          <t>5,02; 8,38</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>13,29; 17,68</t>
+          <t>13,3; 17,41</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>15,45; 20,32</t>
+          <t>15,8; 20,75</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>20,43; 33,45</t>
+          <t>20,27; 33,17</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,31; 7,64</t>
+          <t>4,31; 7,55</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>16,06; 22,97</t>
+          <t>15,92; 23,23</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18,62; 24,79</t>
+          <t>18,53; 25,12</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>22,32; 41,09</t>
+          <t>22,18; 41,65</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,83; 13,08</t>
+          <t>4,85; 11,68</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,01; 32,79</t>
+          <t>19,08; 32,83</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>24,11; 33,34</t>
+          <t>24,36; 33,74</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>19,93; 33,34</t>
+          <t>19,78; 33,37</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,96; 8,67</t>
+          <t>5,01; 8,75</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18,41; 25,2</t>
+          <t>18,39; 26,08</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>22,17; 27,7</t>
+          <t>21,83; 27,8</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>22,42; 34,68</t>
+          <t>22,91; 34,24</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,02; 8,89</t>
+          <t>5,08; 8,78</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>13,74; 16,59</t>
+          <t>13,74; 16,52</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18,12; 21,33</t>
+          <t>18,23; 21,43</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17,54; 25,22</t>
+          <t>17,51; 25,29</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,37; 11,57</t>
+          <t>6,21; 10,69</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,38; 20,92</t>
+          <t>16,35; 21,01</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,54; 25,21</t>
+          <t>20,8; 25,22</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>20,5; 27,04</t>
+          <t>20,39; 26,96</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,95; 8,68</t>
+          <t>5,93; 8,74</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15,28; 17,63</t>
+          <t>15,25; 17,63</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19,8; 22,59</t>
+          <t>19,8; 22,52</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>19,92; 24,68</t>
+          <t>19,81; 24,9</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q61A-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Q61A-Habitat-trans_orig.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10,88</t>
+          <t>11,21</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>18,74</t>
+          <t>18,24</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>15,82</t>
+          <t>15,63</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,27; 5,78</t>
+          <t>3,25; 5,58</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10,75; 18,17</t>
+          <t>10,83; 19,21</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15,18; 23,05</t>
+          <t>15,91; 23,94</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7,44; 16,99</t>
+          <t>7,55; 16,74</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,0; 7,76</t>
+          <t>4,91; 7,85</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,92; 22,3</t>
+          <t>13,88; 22,25</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,61; 24,52</t>
+          <t>14,79; 24,59</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>15,14; 24,52</t>
+          <t>14,59; 23,38</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,48; 6,46</t>
+          <t>4,48; 6,43</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12,86; 18,3</t>
+          <t>12,75; 18,5</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15,93; 21,82</t>
+          <t>16,01; 21,92</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>12,73; 19,5</t>
+          <t>12,7; 19,64</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>18,57</t>
+          <t>18,3</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>20,39</t>
+          <t>20,42</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>19,68</t>
+          <t>19,58</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,72; 16,25</t>
+          <t>4,73; 14,85</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>12,8; 17,69</t>
+          <t>12,64; 17,39</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17,95; 24,05</t>
+          <t>17,66; 23,97</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13,42; 26,22</t>
+          <t>13,75; 25,73</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,07; 21,48</t>
+          <t>7,31; 20,23</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,48; 18,43</t>
+          <t>13,35; 18,2</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,68; 28,21</t>
+          <t>19,71; 28,86</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>16,16; 27,32</t>
+          <t>16,15; 26,59</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,74; 14,81</t>
+          <t>6,72; 14,84</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13,63; 17,06</t>
+          <t>13,58; 16,85</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19,71; 24,67</t>
+          <t>19,44; 24,55</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>16,24; 24,91</t>
+          <t>15,99; 24,15</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>21,06</t>
+          <t>20,6</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>30,15</t>
+          <t>30,34</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>25,43</t>
+          <t>25,39</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,81; 9,75</t>
+          <t>4,93; 9,64</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12,04; 17,23</t>
+          <t>12,18; 16,81</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13,72; 19,53</t>
+          <t>13,72; 19,66</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>16,29; 29,91</t>
+          <t>15,44; 27,95</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,08; 8,03</t>
+          <t>4,11; 7,97</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,54; 20,81</t>
+          <t>13,61; 20,87</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>16,17; 24,36</t>
+          <t>15,76; 23,96</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>21,99; 43,59</t>
+          <t>22,75; 41,97</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,02; 8,38</t>
+          <t>4,9; 8,27</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>13,3; 17,41</t>
+          <t>13,31; 17,43</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>15,8; 20,75</t>
+          <t>15,48; 20,51</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>20,27; 33,17</t>
+          <t>21,07; 32,15</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>29,53</t>
+          <t>27,79</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>25,22</t>
+          <t>26,0</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>27,26</t>
+          <t>26,84</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,31; 7,55</t>
+          <t>4,24; 7,55</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15,92; 23,23</t>
+          <t>16,13; 22,68</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18,53; 25,12</t>
+          <t>18,53; 24,68</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>22,18; 41,65</t>
+          <t>20,9; 37,75</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,85; 11,68</t>
+          <t>5,0; 12,69</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,08; 32,83</t>
+          <t>18,72; 32,77</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>24,36; 33,74</t>
+          <t>24,36; 33,25</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>19,78; 33,37</t>
+          <t>20,3; 34,79</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,01; 8,75</t>
+          <t>4,94; 8,75</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18,39; 26,08</t>
+          <t>18,1; 25,44</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>21,83; 27,8</t>
+          <t>22,34; 27,75</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>22,91; 34,24</t>
+          <t>22,23; 33,35</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>20,87</t>
+          <t>20,29</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>23,15</t>
+          <t>23,36</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>22,15</t>
+          <t>22,02</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,08; 8,78</t>
+          <t>5,02; 8,57</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>13,74; 16,52</t>
+          <t>13,76; 16,62</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18,23; 21,43</t>
+          <t>18,09; 21,41</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17,51; 25,29</t>
+          <t>17,37; 24,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,21; 10,69</t>
+          <t>6,23; 11,24</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,35; 21,01</t>
+          <t>16,42; 20,71</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,8; 25,22</t>
+          <t>20,77; 25,34</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>20,39; 26,96</t>
+          <t>20,59; 26,76</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,93; 8,74</t>
+          <t>5,91; 8,75</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15,25; 17,63</t>
+          <t>15,23; 17,64</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19,8; 22,52</t>
+          <t>19,72; 22,55</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>19,81; 24,9</t>
+          <t>19,66; 24,45</t>
         </is>
       </c>
     </row>
